--- a/artfynd/A 28492-2022 artfynd.xlsx
+++ b/artfynd/A 28492-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28492-2022 artfynd.xlsx
+++ b/artfynd/A 28492-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56494731</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570402.4141089071</v>
+        <v>570402</v>
       </c>
       <c r="R2" t="n">
-        <v>7107022.268123435</v>
+        <v>7107022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-05-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>56494729</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570338.3767563029</v>
+        <v>570338</v>
       </c>
       <c r="R3" t="n">
-        <v>7107024.75612719</v>
+        <v>7107025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2015-05-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,12 +906,7 @@
         <v>56494730</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570402.4141089071</v>
+        <v>570402</v>
       </c>
       <c r="R4" t="n">
-        <v>7107022.268123435</v>
+        <v>7107022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +971,9 @@
           <t>2015-05-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 28492-2022 artfynd.xlsx
+++ b/artfynd/A 28492-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56494731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56494729</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56494730</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>